--- a/data_result/2026-05-17/summary.xlsx
+++ b/data_result/2026-05-17/summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="test_task" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_task" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -615,22 +615,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>2.3890±0.0275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>4.9790±0.0863</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>17.3258±0.0612</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>26.5663±0.0882</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>35.2592±0.2144</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>54.8776±0.3557</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -673,22 +673,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>5.4221±0.0745</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>9.9866±0.0489</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>2.5596±0.0338</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>5.1686±0.1162</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -713,22 +713,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>37.4185±0.6422</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>57.5491±0.7012</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>24.5855±0.1699</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>38.8147±0.3890</t>
         </is>
       </c>
     </row>
@@ -741,32 +741,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-0.3451</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-0.3723</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-0.1706</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-0.1896</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-2.2417</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-2.9441</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-2.1593</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-2.6715</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-2.9680</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-3.3957</t>
         </is>
       </c>
     </row>
@@ -809,32 +809,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-6.80%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-3.87%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-7.14%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-12.94%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-11.08%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-6.12%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-4.87%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-13.73%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-9.59%</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>5.2979±0.1199</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>10.4838±0.3554</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-0.2454</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-0.2205</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-4.86%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
